--- a/CSAUDE Concurso FRIO.xlsx
+++ b/CSAUDE Concurso FRIO.xlsx
@@ -799,6 +799,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -810,18 +822,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="11"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1241,31 +1241,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
       <c r="M1" s="7">
         <v>0.16</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
       <c r="H2" s="70" t="s">
         <v>19</v>
       </c>
@@ -1315,12 +1315,12 @@
       <c r="B5" s="49"/>
       <c r="C5" s="41"/>
       <c r="D5" s="39"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
       <c r="K5" s="30"/>
       <c r="O5" s="1"/>
     </row>
@@ -1357,17 +1357,17 @@
       <c r="O7" s="1"/>
     </row>
     <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
       <c r="E8" s="60"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="65"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="69"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
@@ -1498,19 +1498,19 @@
         <v>7</v>
       </c>
       <c r="H12" s="23">
-        <v>25055.439999999999</v>
+        <v>24668.25</v>
       </c>
       <c r="I12" s="23">
         <f t="shared" ref="I12:I15" si="0">+H12*F12</f>
-        <v>150332.63999999998</v>
+        <v>148009.5</v>
       </c>
       <c r="J12" s="24">
         <f>16%*I12</f>
-        <v>24053.222399999999</v>
+        <v>23681.52</v>
       </c>
       <c r="K12" s="25">
         <f>J12+I12</f>
-        <v>174385.86239999998</v>
+        <v>171691.02</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="47.25" x14ac:dyDescent="0.25">
@@ -1536,19 +1536,19 @@
         <v>7</v>
       </c>
       <c r="H13" s="23">
-        <v>905258.35</v>
+        <v>890821.09</v>
       </c>
       <c r="I13" s="23">
         <f t="shared" si="0"/>
-        <v>3621033.4</v>
+        <v>3563284.36</v>
       </c>
       <c r="J13" s="24">
         <f>16%*I13</f>
-        <v>579365.34400000004</v>
+        <v>570125.4976</v>
       </c>
       <c r="K13" s="25">
         <f t="shared" ref="K13:K15" si="1">J13+I13</f>
-        <v>4200398.7439999999</v>
+        <v>4133409.8575999998</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="47.25" x14ac:dyDescent="0.25">
@@ -1612,19 +1612,19 @@
         <v>7</v>
       </c>
       <c r="H15" s="23">
-        <v>13450.82</v>
+        <v>13242.97</v>
       </c>
       <c r="I15" s="23">
         <f t="shared" si="0"/>
-        <v>13450.82</v>
+        <v>13242.97</v>
       </c>
       <c r="J15" s="24">
         <f>16%*I15</f>
-        <v>2152.1311999999998</v>
+        <v>2118.8751999999999</v>
       </c>
       <c r="K15" s="25">
         <f t="shared" si="1"/>
-        <v>15602.9512</v>
+        <v>15361.8452</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1638,15 +1638,15 @@
       <c r="H16" s="13"/>
       <c r="I16" s="11">
         <f>SUM(I11:I15)</f>
-        <v>4186376.4299999997</v>
+        <v>4126096.4</v>
       </c>
       <c r="J16" s="6">
         <f>SUM(J11:J15)</f>
-        <v>669820.22879999992</v>
+        <v>660175.424</v>
       </c>
       <c r="K16" s="10">
         <f>SUM(K11:K15)</f>
-        <v>4856196.6588000003</v>
+        <v>4786271.824</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
